--- a/UI/arquivos/dados_validado.xlsx
+++ b/UI/arquivos/dados_validado.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="83">
   <si>
     <t>Matrícula</t>
   </si>
@@ -28,292 +28,241 @@
     <t>cargo</t>
   </si>
   <si>
-    <t>Victor Eduardo De Sousa</t>
-  </si>
-  <si>
-    <t>Lucas Moreira Costa</t>
-  </si>
-  <si>
-    <t>Marcelo Silva Martins</t>
-  </si>
-  <si>
-    <t>Lincoln Moises Alves</t>
-  </si>
-  <si>
-    <t>Pedro Paulo Lima Da Silva</t>
-  </si>
-  <si>
-    <t>Gustavo Augusto Santos</t>
-  </si>
-  <si>
-    <t>Leonardo Henrique</t>
-  </si>
-  <si>
-    <t>Wesley Almeida Medeiros</t>
-  </si>
-  <si>
-    <t>Ramon De Oliveira Mendes</t>
-  </si>
-  <si>
-    <t>Iago Luann Pereira</t>
-  </si>
-  <si>
-    <t>Daniel Eudes De Lima</t>
-  </si>
-  <si>
-    <t>Arthur Thomas Dos Santos</t>
-  </si>
-  <si>
-    <t>Luiz Henrique Dias Macedo</t>
-  </si>
-  <si>
-    <t>Luiz Paulo De Oliveira</t>
-  </si>
-  <si>
-    <t>Luiz Gabriel Silva Lima</t>
-  </si>
-  <si>
-    <t>Keila Yanka Souza</t>
-  </si>
-  <si>
-    <t>Gustavo Vieira Da Silva</t>
-  </si>
-  <si>
-    <t>Glaucia Bispo Dos Santos</t>
-  </si>
-  <si>
-    <t>Joao Victor Silverio</t>
-  </si>
-  <si>
-    <t>Daniel Nunes Dos Santos</t>
-  </si>
-  <si>
-    <t>Kelvy Batista Diniz</t>
-  </si>
-  <si>
-    <t>Maria Edileusa Lopes</t>
-  </si>
-  <si>
-    <t>Arnaldo Borges De Lima</t>
-  </si>
-  <si>
-    <t>Julio Cesar Faustino</t>
-  </si>
-  <si>
-    <t>Joao Vitor Batista</t>
-  </si>
-  <si>
-    <t>Enzo Veloso Santana</t>
-  </si>
-  <si>
-    <t>Ian Cleber Sousa</t>
-  </si>
-  <si>
-    <t>Pedro Augusto Machado</t>
-  </si>
-  <si>
-    <t>Raphael Rodrigues</t>
-  </si>
-  <si>
-    <t>Andre Pereira Ribeiro</t>
-  </si>
-  <si>
-    <t>Gleyce Kelly Ventura</t>
-  </si>
-  <si>
-    <t>Matheus Gomes Alves</t>
-  </si>
-  <si>
-    <t>Ana Clara Da Paz Pereira</t>
-  </si>
-  <si>
-    <t>Gabriel Medeiros</t>
-  </si>
-  <si>
-    <t>Karlos Augusto Ferreira</t>
-  </si>
-  <si>
-    <t>Anna Cristina Soares</t>
-  </si>
-  <si>
-    <t>Kevin Alves Vasconcelos</t>
-  </si>
-  <si>
-    <t>Leticia Carolina Quintas</t>
-  </si>
-  <si>
-    <t>Kathleen Soares Ferreira</t>
-  </si>
-  <si>
-    <t>Victor Camargo Rosas</t>
-  </si>
-  <si>
-    <t>Carlos Jaaziel Da Silva</t>
-  </si>
-  <si>
-    <t>Vinicius Cardoso Sales</t>
-  </si>
-  <si>
-    <t>Edson Wyllon De Oliveira</t>
-  </si>
-  <si>
-    <t>Luiz Otavio Ramos</t>
-  </si>
-  <si>
-    <t>Eduardo Pereira Da Silva</t>
-  </si>
-  <si>
-    <t>Erick Daniel Costa</t>
-  </si>
-  <si>
-    <t>Luana Crispim Gomes</t>
-  </si>
-  <si>
-    <t>Pablo Augusto Costa</t>
-  </si>
-  <si>
-    <t>Yasmin Veras Santos</t>
-  </si>
-  <si>
-    <t>Samuel Pereira Alves</t>
-  </si>
-  <si>
-    <t>Moises Santos Araujo</t>
-  </si>
-  <si>
-    <t>Jessica Soares Costa</t>
-  </si>
-  <si>
-    <t>Kelly Cristina Mota Diniz</t>
-  </si>
-  <si>
-    <t>Thiago Serra De Quadros</t>
-  </si>
-  <si>
-    <t>Fellipe Ribeiro Fernandez</t>
-  </si>
-  <si>
-    <t>Alvaro Jesus Moreno</t>
-  </si>
-  <si>
-    <t>Marta Lopes Ferreira</t>
-  </si>
-  <si>
-    <t>Yuri Dos Santos</t>
-  </si>
-  <si>
-    <t>Alisson Benedito Rocha</t>
-  </si>
-  <si>
-    <t>Fernando Rocha De Sousa</t>
-  </si>
-  <si>
-    <t>Joao Paulo Galdino</t>
-  </si>
-  <si>
-    <t>William Ferreira De Sousa</t>
-  </si>
-  <si>
-    <t>Alexsander Phablo Santos</t>
-  </si>
-  <si>
-    <t>Renato Viana Messias</t>
-  </si>
-  <si>
-    <t>Liu Nascimento Soares</t>
+    <t>Eduardo Da Silva Lopes</t>
+  </si>
+  <si>
+    <t>Flavio Benvenuto Sobrinho</t>
+  </si>
+  <si>
+    <t>Luizera</t>
+  </si>
+  <si>
+    <t>Matheus Dantas Paiva</t>
+  </si>
+  <si>
+    <t>Wildemberg De Melo</t>
+  </si>
+  <si>
+    <t>Jonathan Diego Pereira</t>
+  </si>
+  <si>
+    <t>Eduardo De Moura Santos</t>
+  </si>
+  <si>
+    <t>Carlos Eduardo Alves</t>
+  </si>
+  <si>
+    <t>Khairo Otsuki</t>
+  </si>
+  <si>
+    <t>Joao Pedro De Godoy</t>
+  </si>
+  <si>
+    <t>Joao Vitor Ferreira</t>
+  </si>
+  <si>
+    <t>Joao Marcelino De Araujo</t>
+  </si>
+  <si>
+    <t>Alan Vieira Da Silva</t>
+  </si>
+  <si>
+    <t>Maria Do Socorro Teixeira</t>
+  </si>
+  <si>
+    <t>Pedro Henrique Pereira</t>
+  </si>
+  <si>
+    <t>Vinicius Goncalves</t>
+  </si>
+  <si>
+    <t>Gabriel Dos Santos</t>
+  </si>
+  <si>
+    <t>Ryan Gabriel Neres</t>
+  </si>
+  <si>
+    <t>Thayana Oliveira Santos</t>
+  </si>
+  <si>
+    <t>Kelvin Clayton Pereira</t>
+  </si>
+  <si>
+    <t>Keneti Alves Da Silva</t>
+  </si>
+  <si>
+    <t>Tallys De Sousa Barbosa</t>
+  </si>
+  <si>
+    <t>Guilherme Antonio</t>
+  </si>
+  <si>
+    <t>Silvio Junior Dos Reis</t>
+  </si>
+  <si>
+    <t>Natanael Aguiar De Souza</t>
+  </si>
+  <si>
+    <t>Bruno Gammerdinger Veras</t>
+  </si>
+  <si>
+    <t>Patricia Dos Santos Leite</t>
+  </si>
+  <si>
+    <t>Guilherme Angel Ribeiro</t>
+  </si>
+  <si>
+    <t>Israel Mauricio</t>
+  </si>
+  <si>
+    <t>Welio Pena Delmonde</t>
+  </si>
+  <si>
+    <t>Gabriel De Sousa Silva</t>
+  </si>
+  <si>
+    <t>Jose Joaquim Pereira</t>
+  </si>
+  <si>
+    <t>Edvaldo Pereira De Jesus</t>
+  </si>
+  <si>
+    <t>Jarson Luiz Carlos</t>
+  </si>
+  <si>
+    <t>Olegario Hesdras Soares</t>
+  </si>
+  <si>
+    <t>Matheus Teixeira De Jesus</t>
+  </si>
+  <si>
+    <t>Luan Henrique Soares</t>
+  </si>
+  <si>
+    <t>Vitor De Souza Vieira</t>
+  </si>
+  <si>
+    <t>Ana Luiza Santos Unruh</t>
+  </si>
+  <si>
+    <t>Johnny Alves De Sousa</t>
+  </si>
+  <si>
+    <t>Pedro Henrique Mendonca</t>
+  </si>
+  <si>
+    <t>Yuk Wendel Dos Santos</t>
+  </si>
+  <si>
+    <t>Lucas Luis Fernandes</t>
+  </si>
+  <si>
+    <t>Mauro Amorim Dalbuquerque</t>
+  </si>
+  <si>
+    <t>Juliana Inacio Alves</t>
+  </si>
+  <si>
+    <t>Desiree Marie Aguiar</t>
+  </si>
+  <si>
+    <t>Ronaldo Severino Da Silva</t>
+  </si>
+  <si>
+    <t>Gustavo Do Nascimento</t>
+  </si>
+  <si>
+    <t>Matheus Dos Reis Rego</t>
+  </si>
+  <si>
+    <t>Pedro Henrique Da Silva</t>
+  </si>
+  <si>
+    <t>Chirleide Lima De Matos</t>
+  </si>
+  <si>
+    <t>Jonathan Douglas</t>
+  </si>
+  <si>
+    <t>Luiz Claudio Da Cruz</t>
+  </si>
+  <si>
+    <t>Jefferson Magalhaes</t>
   </si>
   <si>
     <t>Logística - CD</t>
   </si>
   <si>
-    <t>Vendas Central</t>
-  </si>
-  <si>
-    <t>Garantia - Goiânia</t>
-  </si>
-  <si>
-    <t>Gerente - Planaltina</t>
+    <t>Expedição - Gama</t>
+  </si>
+  <si>
+    <t>Tecnologia</t>
+  </si>
+  <si>
+    <t>Vendas - Ceilândia</t>
+  </si>
+  <si>
+    <t>Inteligencia de Mercado</t>
+  </si>
+  <si>
+    <t>Expedição - SOF</t>
+  </si>
+  <si>
+    <t>Logística - SOF</t>
+  </si>
+  <si>
+    <t>Jurídico</t>
+  </si>
+  <si>
+    <t>Vendas - Planaltina</t>
+  </si>
+  <si>
+    <t>Logística - Ceilândia</t>
+  </si>
+  <si>
+    <t>E-commerce</t>
+  </si>
+  <si>
+    <t>Vendas - Gama</t>
   </si>
   <si>
     <t>Crédito, cadastro e cobrança</t>
   </si>
   <si>
+    <t>Serviços Gerais - SOF</t>
+  </si>
+  <si>
     <t>Logística - Goiânia</t>
   </si>
   <si>
-    <t>Vendas - Gama</t>
-  </si>
-  <si>
-    <t>Vendas - Planaltina</t>
+    <t>Vendas - Asa Norte</t>
+  </si>
+  <si>
+    <t>Gente e Gestão</t>
+  </si>
+  <si>
+    <t>Logística - Gama</t>
   </si>
   <si>
     <t>Vendas - SOF</t>
   </si>
   <si>
+    <t>Logística - Planaltina</t>
+  </si>
+  <si>
+    <t>Logística - Recife</t>
+  </si>
+  <si>
+    <t>Compras</t>
+  </si>
+  <si>
+    <t>Logística - Asa Norte</t>
+  </si>
+  <si>
+    <t>Vendas - Goiânia</t>
+  </si>
+  <si>
     <t>Inteligência Comercial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expedição - Ferista </t>
-  </si>
-  <si>
-    <t>Logística - Asa Norte</t>
-  </si>
-  <si>
-    <t>Almoxarifado e Arquivo</t>
-  </si>
-  <si>
-    <t>Marketing</t>
-  </si>
-  <si>
-    <t>E-commerce</t>
-  </si>
-  <si>
-    <t>Logística - Ceilândia</t>
-  </si>
-  <si>
-    <t>Serviços Gerais - SOF</t>
-  </si>
-  <si>
-    <t>Logística - Gama</t>
-  </si>
-  <si>
-    <t>Serviços Gerais- Gama</t>
-  </si>
-  <si>
-    <t>Logística - SOF</t>
-  </si>
-  <si>
-    <t>Vendas - Goiânia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logística - Ferista </t>
-  </si>
-  <si>
-    <t>Inteligência Logística</t>
-  </si>
-  <si>
-    <t>Vendas - Ceilândia</t>
-  </si>
-  <si>
-    <t>Gente e Gestão</t>
-  </si>
-  <si>
-    <t>Caixa - Ceilândia</t>
-  </si>
-  <si>
-    <t>Logística - Planaltina</t>
-  </si>
-  <si>
-    <t>Logística - Recife</t>
-  </si>
-  <si>
-    <t>Caixa - Planaltina</t>
-  </si>
-  <si>
-    <t>Departamento Pessoal</t>
-  </si>
-  <si>
-    <t>Expedição - Asa Norte</t>
   </si>
 </sst>
 </file>
@@ -645,7 +594,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -664,7 +613,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2">
-        <v>8579</v>
+        <v>8841</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
@@ -673,26 +622,26 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3">
-        <v>6278</v>
+        <v>6343</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4">
-        <v>7633</v>
+        <v>8720</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
@@ -701,54 +650,54 @@
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5">
-        <v>6646</v>
+        <v>8101</v>
       </c>
       <c r="B5" t="s">
         <v>7</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D5" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6">
-        <v>8177</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
         <v>8</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7">
-        <v>7683</v>
+        <v>7956</v>
       </c>
       <c r="B7" t="s">
         <v>9</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8">
-        <v>4986</v>
+        <v>7340</v>
       </c>
       <c r="B8" t="s">
         <v>10</v>
@@ -757,26 +706,26 @@
         <v>6</v>
       </c>
       <c r="D8" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9">
-        <v>4370</v>
+        <v>8528</v>
       </c>
       <c r="B9" t="s">
         <v>11</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10">
-        <v>2944</v>
+        <v>1321</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
@@ -785,82 +734,82 @@
         <v>7</v>
       </c>
       <c r="D10" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11">
-        <v>4942</v>
+        <v>8079</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
       </c>
       <c r="C11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D11" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12">
-        <v>8851</v>
+        <v>2179</v>
       </c>
       <c r="B12" t="s">
         <v>14</v>
       </c>
       <c r="C12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D12" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13">
-        <v>8838</v>
+        <v>8261</v>
       </c>
       <c r="B13" t="s">
         <v>15</v>
       </c>
       <c r="C13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D13" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14">
-        <v>6179</v>
+        <v>6324</v>
       </c>
       <c r="B14" t="s">
         <v>16</v>
       </c>
       <c r="C14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D14" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15">
-        <v>8289</v>
+        <v>1060</v>
       </c>
       <c r="B15" t="s">
         <v>17</v>
       </c>
       <c r="C15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D15" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16">
-        <v>8728</v>
+        <v>8418</v>
       </c>
       <c r="B16" t="s">
         <v>18</v>
@@ -869,12 +818,12 @@
         <v>9</v>
       </c>
       <c r="D16" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17">
-        <v>6483</v>
+        <v>3122</v>
       </c>
       <c r="B17" t="s">
         <v>19</v>
@@ -883,12 +832,12 @@
         <v>10</v>
       </c>
       <c r="D17" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18">
-        <v>8843</v>
+        <v>4369</v>
       </c>
       <c r="B18" t="s">
         <v>20</v>
@@ -897,12 +846,12 @@
         <v>10</v>
       </c>
       <c r="D18" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19">
-        <v>8216</v>
+        <v>8568</v>
       </c>
       <c r="B19" t="s">
         <v>21</v>
@@ -911,12 +860,12 @@
         <v>11</v>
       </c>
       <c r="D19" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20">
-        <v>6657</v>
+        <v>8815</v>
       </c>
       <c r="B20" t="s">
         <v>22</v>
@@ -925,12 +874,12 @@
         <v>11</v>
       </c>
       <c r="D20" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21">
-        <v>4398</v>
+        <v>8766</v>
       </c>
       <c r="B21" t="s">
         <v>23</v>
@@ -939,12 +888,12 @@
         <v>11</v>
       </c>
       <c r="D21" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22">
-        <v>6430</v>
+        <v>5002</v>
       </c>
       <c r="B22" t="s">
         <v>24</v>
@@ -953,40 +902,40 @@
         <v>11</v>
       </c>
       <c r="D22" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23">
-        <v>3886</v>
+        <v>1851</v>
       </c>
       <c r="B23" t="s">
         <v>25</v>
       </c>
       <c r="C23">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D23" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24">
-        <v>7046</v>
+        <v>8194</v>
       </c>
       <c r="B24" t="s">
         <v>26</v>
       </c>
       <c r="C24">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25">
-        <v>8160</v>
+        <v>7392</v>
       </c>
       <c r="B25" t="s">
         <v>27</v>
@@ -995,12 +944,12 @@
         <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26">
-        <v>6294</v>
+        <v>4661</v>
       </c>
       <c r="B26" t="s">
         <v>28</v>
@@ -1009,26 +958,26 @@
         <v>13</v>
       </c>
       <c r="D26" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27">
-        <v>8475</v>
+        <v>7285</v>
       </c>
       <c r="B27" t="s">
         <v>29</v>
       </c>
       <c r="C27">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D27" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28">
-        <v>8699</v>
+        <v>6757</v>
       </c>
       <c r="B28" t="s">
         <v>30</v>
@@ -1037,12 +986,12 @@
         <v>15</v>
       </c>
       <c r="D28" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29">
-        <v>8362</v>
+        <v>7752</v>
       </c>
       <c r="B29" t="s">
         <v>31</v>
@@ -1051,12 +1000,12 @@
         <v>16</v>
       </c>
       <c r="D29" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30">
-        <v>8251</v>
+        <v>5064</v>
       </c>
       <c r="B30" t="s">
         <v>32</v>
@@ -1065,40 +1014,40 @@
         <v>17</v>
       </c>
       <c r="D30" t="s">
-        <v>89</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31">
-        <v>3709</v>
+        <v>8565</v>
       </c>
       <c r="B31" t="s">
         <v>33</v>
       </c>
       <c r="C31">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D31" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32">
-        <v>2281</v>
+        <v>8543</v>
       </c>
       <c r="B32" t="s">
         <v>34</v>
       </c>
       <c r="C32">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D32" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33">
-        <v>6482</v>
+        <v>2446</v>
       </c>
       <c r="B33" t="s">
         <v>35</v>
@@ -1112,21 +1061,21 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34">
-        <v>8630</v>
+        <v>8698</v>
       </c>
       <c r="B34" t="s">
         <v>36</v>
       </c>
       <c r="C34">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D34" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35">
-        <v>6610</v>
+        <v>8625</v>
       </c>
       <c r="B35" t="s">
         <v>37</v>
@@ -1135,40 +1084,40 @@
         <v>19</v>
       </c>
       <c r="D35" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36">
-        <v>3816</v>
+        <v>8758</v>
       </c>
       <c r="B36" t="s">
         <v>38</v>
       </c>
       <c r="C36">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D36" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37">
-        <v>8684</v>
+        <v>7310</v>
       </c>
       <c r="B37" t="s">
         <v>39</v>
       </c>
       <c r="C37">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D37" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38">
-        <v>6514</v>
+        <v>7236</v>
       </c>
       <c r="B38" t="s">
         <v>40</v>
@@ -1177,12 +1126,12 @@
         <v>21</v>
       </c>
       <c r="D38" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39">
-        <v>3382</v>
+        <v>7471</v>
       </c>
       <c r="B39" t="s">
         <v>41</v>
@@ -1191,26 +1140,26 @@
         <v>21</v>
       </c>
       <c r="D39" t="s">
-        <v>93</v>
+        <v>67</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40">
-        <v>8674</v>
+        <v>8272</v>
       </c>
       <c r="B40" t="s">
         <v>42</v>
       </c>
       <c r="C40">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D40" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41">
-        <v>8011</v>
+        <v>2395</v>
       </c>
       <c r="B41" t="s">
         <v>43</v>
@@ -1219,68 +1168,68 @@
         <v>23</v>
       </c>
       <c r="D41" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42">
-        <v>8503</v>
+        <v>8821</v>
       </c>
       <c r="B42" t="s">
         <v>44</v>
       </c>
       <c r="C42">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D42" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43">
-        <v>7871</v>
+        <v>8781</v>
       </c>
       <c r="B43" t="s">
         <v>45</v>
       </c>
       <c r="C43">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D43" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44">
-        <v>8747</v>
+        <v>8288</v>
       </c>
       <c r="B44" t="s">
         <v>46</v>
       </c>
       <c r="C44">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D44" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45">
-        <v>8611</v>
+        <v>7699</v>
       </c>
       <c r="B45" t="s">
         <v>47</v>
       </c>
       <c r="C45">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D45" t="s">
-        <v>96</v>
+        <v>58</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46">
-        <v>7100</v>
+        <v>8091</v>
       </c>
       <c r="B46" t="s">
         <v>48</v>
@@ -1289,40 +1238,40 @@
         <v>25</v>
       </c>
       <c r="D46" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47">
-        <v>8001</v>
+        <v>6162</v>
       </c>
       <c r="B47" t="s">
         <v>49</v>
       </c>
       <c r="C47">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D47" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48">
-        <v>7083</v>
+        <v>8586</v>
       </c>
       <c r="B48" t="s">
         <v>50</v>
       </c>
       <c r="C48">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D48" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49">
-        <v>7693</v>
+        <v>7438</v>
       </c>
       <c r="B49" t="s">
         <v>51</v>
@@ -1331,12 +1280,12 @@
         <v>27</v>
       </c>
       <c r="D49" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50">
-        <v>6344</v>
+        <v>3632</v>
       </c>
       <c r="B50" t="s">
         <v>52</v>
@@ -1345,26 +1294,26 @@
         <v>27</v>
       </c>
       <c r="D50" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51">
-        <v>8310</v>
+        <v>7465</v>
       </c>
       <c r="B51" t="s">
         <v>53</v>
       </c>
       <c r="C51">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D51" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52">
-        <v>6917</v>
+        <v>7284</v>
       </c>
       <c r="B52" t="s">
         <v>54</v>
@@ -1373,203 +1322,49 @@
         <v>28</v>
       </c>
       <c r="D52" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53">
-        <v>4581</v>
+        <v>8797</v>
       </c>
       <c r="B53" t="s">
         <v>55</v>
       </c>
       <c r="C53">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D53" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54">
-        <v>6794</v>
+        <v>3400</v>
       </c>
       <c r="B54" t="s">
         <v>56</v>
       </c>
       <c r="C54">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D54" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55">
-        <v>8558</v>
+        <v>2228</v>
       </c>
       <c r="B55" t="s">
         <v>57</v>
       </c>
       <c r="C55">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D55" t="s">
         <v>69</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4">
-      <c r="A56">
-        <v>6220</v>
-      </c>
-      <c r="B56" t="s">
-        <v>58</v>
-      </c>
-      <c r="C56">
-        <v>28</v>
-      </c>
-      <c r="D56" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4">
-      <c r="A57">
-        <v>8753</v>
-      </c>
-      <c r="B57" t="s">
-        <v>59</v>
-      </c>
-      <c r="C57">
-        <v>28</v>
-      </c>
-      <c r="D57" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4">
-      <c r="A58">
-        <v>8870</v>
-      </c>
-      <c r="B58" t="s">
-        <v>60</v>
-      </c>
-      <c r="C58">
-        <v>29</v>
-      </c>
-      <c r="D58" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4">
-      <c r="A59">
-        <v>8784</v>
-      </c>
-      <c r="B59" t="s">
-        <v>61</v>
-      </c>
-      <c r="C59">
-        <v>29</v>
-      </c>
-      <c r="D59" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4">
-      <c r="A60">
-        <v>4848</v>
-      </c>
-      <c r="B60" t="s">
-        <v>62</v>
-      </c>
-      <c r="C60">
-        <v>30</v>
-      </c>
-      <c r="D60" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4">
-      <c r="A61">
-        <v>6194</v>
-      </c>
-      <c r="B61" t="s">
-        <v>63</v>
-      </c>
-      <c r="C61">
-        <v>30</v>
-      </c>
-      <c r="D61" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4">
-      <c r="A62">
-        <v>3190</v>
-      </c>
-      <c r="B62" t="s">
-        <v>64</v>
-      </c>
-      <c r="C62">
-        <v>30</v>
-      </c>
-      <c r="D62" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4">
-      <c r="A63">
-        <v>8609</v>
-      </c>
-      <c r="B63" t="s">
-        <v>65</v>
-      </c>
-      <c r="C63">
-        <v>30</v>
-      </c>
-      <c r="D63" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4">
-      <c r="A64">
-        <v>6974</v>
-      </c>
-      <c r="B64" t="s">
-        <v>66</v>
-      </c>
-      <c r="C64">
-        <v>31</v>
-      </c>
-      <c r="D64" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4">
-      <c r="A65">
-        <v>8560</v>
-      </c>
-      <c r="B65" t="s">
-        <v>67</v>
-      </c>
-      <c r="C65">
-        <v>31</v>
-      </c>
-      <c r="D65" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4">
-      <c r="A66">
-        <v>8644</v>
-      </c>
-      <c r="B66" t="s">
-        <v>68</v>
-      </c>
-      <c r="C66">
-        <v>31</v>
-      </c>
-      <c r="D66" t="s">
-        <v>81</v>
       </c>
     </row>
   </sheetData>
